--- a/payslip-ui/public/Salary_summary.xlsx
+++ b/payslip-ui/public/Salary_summary.xlsx
@@ -16,9 +16,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
-    <t>Pay Bill for the month of July 2026</t>
-  </si>
-  <si>
     <t>Debit Heads:</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>Expenses: PF Employers contribution:</t>
+  </si>
+  <si>
+    <t>Sl.No.</t>
   </si>
 </sst>
 </file>
@@ -167,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -219,17 +219,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -280,10 +269,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -307,56 +295,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -364,6 +307,57 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -681,777 +675,755 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="A1" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="30"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="32"/>
+      <c r="B3" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C3" s="28"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="32"/>
+      <c r="B4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="16">
+        <v>1750041</v>
+      </c>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="32"/>
+      <c r="B5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="34" t="s">
+      <c r="C5" s="19"/>
+      <c r="D5" s="16">
+        <v>67756</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="25"/>
+    </row>
+    <row r="6" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="32"/>
+      <c r="B7" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="32">
-        <v>1750041</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="26"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="32">
-        <v>67756</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="26"/>
-    </row>
-    <row r="6" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="26"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="32">
+      <c r="C7" s="21"/>
+      <c r="D7" s="16">
         <f>D5+D4</f>
         <v>1817797</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
       <c r="I7" s="27"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="12">
+    <row r="8" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
         <v>1</v>
       </c>
+      <c r="B8" s="12">
+        <v>2</v>
+      </c>
+      <c r="C8" s="11">
+        <v>3</v>
+      </c>
       <c r="D8" s="12">
-        <v>2</v>
-      </c>
-      <c r="E8" s="12">
+        <v>4</v>
+      </c>
+      <c r="E8" s="11">
+        <v>5</v>
+      </c>
+      <c r="F8" s="12">
+        <v>6</v>
+      </c>
+      <c r="G8" s="11">
+        <v>7</v>
+      </c>
+      <c r="H8" s="12">
+        <v>8</v>
+      </c>
+      <c r="I8" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="12">
-        <v>4</v>
-      </c>
-      <c r="G8" s="12">
-        <v>5</v>
-      </c>
-      <c r="H8" s="12">
-        <v>6</v>
-      </c>
-      <c r="I8" s="12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>85000</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>41667</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4">
+      <c r="E10" s="2"/>
+      <c r="F10" s="3">
         <v>212</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4">
+      <c r="G10" s="2"/>
+      <c r="H10" s="3">
         <v>268317</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="14">
         <f>SUM(C10:H10)</f>
         <v>395196</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4">
+      <c r="A11" s="11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="3">
         <v>3824</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="14">
         <f t="shared" ref="I11:I24" si="0">SUM(C11:H11)</f>
         <v>3824</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="A12" s="11">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3">
         <v>15300</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>17346</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>5600</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4">
+      <c r="G12" s="2"/>
+      <c r="H12" s="3">
         <v>113328</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
         <v>152174</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="4">
+      <c r="A13" s="11">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3">
         <v>15300</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>3750</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>600</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>3000</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4">
+      <c r="G13" s="2"/>
+      <c r="H13" s="3">
         <v>129524</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
         <v>152174</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="A14" s="11">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3">
         <v>9130</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>3750</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4">
+      <c r="G14" s="2"/>
+      <c r="H14" s="3">
         <v>131022</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
         <v>146402</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4">
+      <c r="A15" s="11">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3">
         <v>3750</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>2000</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="3">
         <v>2000</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4">
+      <c r="G15" s="2"/>
+      <c r="H15" s="3">
         <v>140152</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="14">
         <f t="shared" si="0"/>
         <v>147902</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4">
+      <c r="A16" s="11">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3">
         <v>3750</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>2000</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <v>2000</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4">
+      <c r="G16" s="2"/>
+      <c r="H16" s="3">
         <v>140152</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="14">
         <f t="shared" si="0"/>
         <v>147902</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4">
+      <c r="A17" s="11">
+        <v>8</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3">
         <v>3750</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4">
+      <c r="G17" s="2"/>
+      <c r="H17" s="3">
         <v>29007</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="14">
         <f t="shared" si="0"/>
         <v>36757</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="A18" s="11">
+        <v>9</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3">
         <v>11000</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>32423</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="3">
         <v>2000</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="3">
         <v>600</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4">
+      <c r="G18" s="2"/>
+      <c r="H18" s="3">
         <v>113866</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="14">
         <f t="shared" si="0"/>
         <v>159889</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="A19" s="11">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3">
         <v>13000</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>31694</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="3">
         <v>1000</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="3">
         <v>3000</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4">
+      <c r="G19" s="2"/>
+      <c r="H19" s="3">
         <v>106133</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="14">
         <f t="shared" si="0"/>
         <v>154827</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4">
+      <c r="A20" s="11">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3">
         <v>21143</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4">
+      <c r="G20" s="2"/>
+      <c r="H20" s="3">
         <v>78646</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="14">
         <f t="shared" si="0"/>
         <v>103189</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4">
+      <c r="A21" s="11">
+        <v>12</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3">
         <v>16678</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="3">
         <v>5020</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="3">
         <v>57638</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="14">
         <f t="shared" si="0"/>
         <v>81336</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4">
+      <c r="A22" s="11">
+        <v>13</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3">
         <v>8479</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4">
+      <c r="G22" s="2"/>
+      <c r="H22" s="3">
         <v>51006</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="14">
         <f t="shared" si="0"/>
         <v>61485</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4">
+      <c r="A23" s="11">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="3">
         <v>3750</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="3">
         <v>1400</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4">
+      <c r="G23" s="2"/>
+      <c r="H23" s="3">
         <v>68290</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="14">
         <f t="shared" si="0"/>
         <v>74740</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
-      <c r="B24" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="23">
+      <c r="B24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="14">
         <f>SUM(C10:C23)</f>
         <v>148730</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="14">
         <f t="shared" ref="D24:H24" si="1">SUM(D10:D23)</f>
         <v>191930</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="14">
         <f t="shared" si="1"/>
         <v>14000</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="14">
         <f t="shared" si="1"/>
         <v>27212</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="14">
         <f t="shared" si="1"/>
         <v>5020</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="14">
         <f t="shared" si="1"/>
         <v>1430905</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="14">
         <f t="shared" si="0"/>
         <v>1817797</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="3"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="9"/>
+      <c r="B26" s="8"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="9"/>
+      <c r="B27" s="8"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="9"/>
+      <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="10"/>
+      <c r="B29" s="9"/>
     </row>
     <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="9"/>
+      <c r="B30" s="8"/>
     </row>
     <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="9"/>
+      <c r="B31" s="8"/>
     </row>
     <row r="32" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="9"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="10"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="10"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="10"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="10"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="10"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="10"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="10"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="10"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="10"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="10"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="10"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="9"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="9"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="9"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="10"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="10"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="10"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="B50" s="10"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="10"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="10"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="10"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="10"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="10"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="10"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="10"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="10"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="9"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="9"/>
-    </row>
-    <row r="61" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="9"/>
-    </row>
-    <row r="62" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="9"/>
-    </row>
-    <row r="63" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="9"/>
-    </row>
-    <row r="64" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
-      <c r="B64" s="9"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="8"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
-      <c r="B66" s="8"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
-      <c r="B67" s="8"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="2"/>
-      <c r="B68" s="8"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
-      <c r="B69" s="8"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="2"/>
-      <c r="B70" s="8"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
-      <c r="B71" s="8"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="2"/>
-      <c r="B72" s="8"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="B73" s="8"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
-      <c r="B74" s="8"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
-      <c r="B75" s="8"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="2"/>
-      <c r="B76" s="8"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="2"/>
-      <c r="B77" s="8"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="2"/>
-      <c r="B78" s="9"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="2"/>
-      <c r="B79" s="10"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
-      <c r="B80" s="9"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
-      <c r="B81" s="9"/>
+      <c r="B32" s="8"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="9"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="9"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="9"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="9"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="9"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="9"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="9"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="9"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="9"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="9"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="9"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="8"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="8"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="8"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="9"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="9"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="9"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="9"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="9"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="9"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="9"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="9"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="9"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="9"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="9"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="9"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="8"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="8"/>
+    </row>
+    <row r="61" spans="2:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="8"/>
+    </row>
+    <row r="62" spans="2:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="8"/>
+    </row>
+    <row r="63" spans="2:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="8"/>
+    </row>
+    <row r="64" spans="2:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="8"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="7"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="7"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="7"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="7"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="7"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="7"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="7"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="7"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="7"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="7"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="7"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="7"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="7"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="8"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="9"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="8"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A7"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E3:I7"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.86614173228346458" right="0.47244094488188981" top="0.19685039370078741" bottom="0.15748031496062992" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait" r:id="rId1"/>
